--- a/erp-server/erp-server-scm/src/main/resources/excel/assetNoticeTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/assetNoticeTemplate.xlsx
@@ -29,21 +29,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>*模具名称</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>序号</t>
+    </r>
   </si>
   <si>
-    <t>*模具标识</t>
-  </si>
-  <si>
-    <t>项目编号</t>
-  </si>
-  <si>
-    <t>*序号</t>
-  </si>
-  <si>
-    <t>*申请日期</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>申请日期</t>
+    </r>
   </si>
   <si>
     <t>申请人</t>
@@ -52,7 +81,26 @@
     <t>申请部门</t>
   </si>
   <si>
-    <t>*模具编码</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>模具编码</t>
+    </r>
   </si>
   <si>
     <t>是否加急</t>
@@ -61,10 +109,48 @@
     <t>计划交期</t>
   </si>
   <si>
-    <t>*申请数量</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>申请数量</t>
+    </r>
   </si>
   <si>
-    <t>*采购组织</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>采购组织</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
@@ -80,7 +166,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,14 +175,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -582,150 +675,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1039,10 +1135,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1052,10 +1148,10 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1067,28 +1163,31 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/assetNoticeTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/assetNoticeTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="13905" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
       <rPr>
@@ -79,6 +79,34 @@
   </si>
   <si>
     <t>申请部门</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>采购开发</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>采购跟单</t>
+    </r>
   </si>
   <si>
     <r>
@@ -166,7 +194,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,6 +365,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1135,10 +1169,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1154,40 +1188,48 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
